--- a/workspace/sheets/invoice_register.xlsx
+++ b/workspace/sheets/invoice_register.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$1:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$1:$L$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,21 +433,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,29 +518,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kowloon Bay Properties Ltd</t>
+          <t>Harbourview Capital Partners III LP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KBP/R/2607</t>
+          <t>HCP3-MF-2026Q3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>80000</v>
+        <v>37500</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1</v>
+        <v>7.82</v>
       </c>
       <c r="H2" s="3">
         <f>ROUND(F2*G2,2)</f>
@@ -548,11 +548,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46211</v>
+        <v>46234</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-07/KBP rent Jul26.pdf</t>
+          <t>docs/invoices/2026-07/Harbourview fee HCP3-MF-2026Q3.pdf</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CloudDesk Inc.</t>
+          <t>Meridian Fine Art Insurance Ltd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CD-10011</t>
+          <t>MAI-10099</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1450</v>
+        <v>2450</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>7.82</v>
@@ -601,7 +601,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-07/invoice_CD-10011.pdf</t>
+          <t>docs/invoices/2026-07/Meridian MAI-10099.pdf</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pacific Freight Logistics Ltd</t>
+          <t>Peak Estates Property Management Ltd</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>INV-2204</t>
+          <t>INV-PM-2204</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23925</v>
+        <v>23200</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>1</v>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-07/Pacific Freight INV-2204.pdf</t>
+          <t>docs/invoices/2026-07/Peak Estates INV-PM-2204.pdf</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shenzhen Parts Co., Ltd.</t>
+          <t>Pearl River Growth Fund II LP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SP-2026-0816</t>
+          <t>PRG2-DN-017</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>309510</v>
+        <v>3000000</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>1.083</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46271</v>
+        <v>46225</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -720,39 +720,39 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-07/INV-SP-2026-0816.pdf</t>
+          <t>docs/invoices/2026-07/Pearl River call PRG2-DN-017.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dongguan Precision Electronics Co., Ltd.</t>
+          <t>Peak Estates Property Management Ltd</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPE/INV/0361</t>
+          <t>INV-PM-2247</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>33980</v>
+        <v>17300</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.82</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <f>ROUND(F6*G6,2)</f>
@@ -760,11 +760,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-07/DPE-INV-0361.pdf</t>
+          <t>docs/invoices/2026-08/Peak Estates INV-PM-2247.pdf</t>
         </is>
       </c>
     </row>
@@ -783,29 +783,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pacific Freight Logistics Ltd</t>
+          <t>Meridian Fine Art Insurance Ltd</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INV-2247</t>
+          <t>MAI-10110</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>33180</v>
+        <v>2450</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>7.81</v>
       </c>
       <c r="H7" s="3">
         <f>ROUND(F7*G7,2)</f>
@@ -813,11 +813,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46267</v>
+        <v>46252</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -826,39 +826,39 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-08/Pacific Freight INV-2247.pdf</t>
+          <t>docs/invoices/2026-08/Meridian MAI-10110.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kowloon Bay Properties Ltd</t>
+          <t>Harbourview Capital Partners III LP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KBP/L/2608</t>
+          <t>HCP3-CN-2026-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>12000</v>
+        <v>500000</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>7.81</v>
       </c>
       <c r="H8" s="3">
         <f>ROUND(F8*G8,2)</f>
@@ -866,11 +866,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -879,27 +879,27 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-08/KBP storage Aug26.pdf</t>
+          <t>docs/invoices/2026-08/Harbourview call HCP3-CN-2026-03.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kowloon Bay Properties Ltd</t>
+          <t>Peak Estates Property Management Ltd</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KBP/R/2608</t>
+          <t>INV-PM-2291</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>80000</v>
+        <v>23200</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>1</v>
@@ -919,26 +919,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46244</v>
+        <v>46296</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-08/KBP rent Aug26.pdf</t>
+          <t>docs/invoices/2026-09/Peak Estates INV-PM-2291.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -947,12 +947,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CloudDesk Inc.</t>
+          <t>Meridian Fine Art Insurance Ltd</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CD-10022</t>
+          <t>MAI-10121</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1450</v>
+        <v>2450</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.81</v>
+        <v>7.8</v>
       </c>
       <c r="H10" s="3">
         <f>ROUND(F10*G10,2)</f>
@@ -972,11 +972,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46252</v>
+        <v>46281</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -985,436 +985,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>docs/invoices/2026-08/invoice_CD-10022.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Shenzhen Parts Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SP-2026-0842</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RMB</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>294780</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1.082</v>
-      </c>
-      <c r="H11" s="3">
-        <f>ROUND(F11*G11,2)</f>
-        <v/>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-08/INV-SP-2026-0842.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dongguan Precision Electronics Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DPE/INV/0370</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>37750</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="H12" s="3">
-        <f>ROUND(F12*G12,2)</f>
-        <v/>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>46281</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-08/DPE-INV-0370.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pacific Freight Logistics Ltd</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INV-2291</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>27660</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <f>ROUND(F13*G13,2)</f>
-        <v/>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/Pacific Freight INV-2291.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Kowloon Bay Properties Ltd</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>KBP/R/2609</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <f>ROUND(F14*G14,2)</f>
-        <v/>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/KBP rent Sep26.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CloudDesk Inc.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CD-10033</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H15" s="3">
-        <f>ROUND(F15*G15,2)</f>
-        <v/>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>46281</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/invoice_CD-10033.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kowloon Bay Properties Ltd</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>KBP/L/2609</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <f>ROUND(F16*G16,2)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/KBP storage Sep26.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Shenzhen Parts Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SP-2026-0865</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RMB</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>332870</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H17" s="3">
-        <f>ROUND(F17*G17,2)</f>
-        <v/>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>46333</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/INV-SP-2026-0865.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Dongguan Precision Electronics Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DPE/INV/0379</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>35350</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H18" s="3">
-        <f>ROUND(F18*G18,2)</f>
-        <v/>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>docs/invoices/2026-09/DPE-INV-0379.pdf</t>
+          <t>docs/invoices/2026-09/Meridian MAI-10121.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>